--- a/results/Int Task Remove ACC -0.9/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_4_permute.xlsx
@@ -440,27 +440,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7168112427519329</v>
+        <v>0.7211725162543026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7170998345500419</v>
+        <v>0.7209203486637219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7181072790976883</v>
+        <v>0.6989826438651128</v>
       </c>
     </row>
     <row r="5">
@@ -470,657 +470,657 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7229326110132794</v>
+        <v>0.6986849460151217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7177510923759931</v>
+        <v>0.690429084169339</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7259237739401607</v>
+        <v>0.6880151048386758</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7242312741047701</v>
+        <v>0.6790806670112957</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7331448730826507</v>
+        <v>0.6766511023226036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7308934017548063</v>
+        <v>0.6768967906070374</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7288849919656604</v>
+        <v>0.6752393140481163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7399330845279772</v>
+        <v>0.6769162285254781</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.719889438520841</v>
+        <v>0.6701747731542382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.719889438520841</v>
+        <v>0.6701747731542382</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7216430539736709</v>
+        <v>0.6700304772551837</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7224815112123517</v>
+        <v>0.6627444099348427</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7310324441623903</v>
+        <v>0.6602225589126534</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7313119299086173</v>
+        <v>0.6538008660555805</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7214064717411192</v>
+        <v>0.6596544813683174</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7234551582982049</v>
+        <v>0.6562330574900079</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7234551582982049</v>
+        <v>0.6587549085121972</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7272665663600029</v>
+        <v>0.6587549085121972</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7263267167359426</v>
+        <v>0.6596024718027601</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7169164876977239</v>
+        <v>0.6561992600282147</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6777834048508639</v>
+        <v>0.6561992600282147</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.683161228952762</v>
+        <v>0.6386462943272099</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6914391554627205</v>
+        <v>0.6207371419045098</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6813711892924037</v>
+        <v>0.6126866915752209</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6751289907272373</v>
+        <v>0.6007637175666949</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6739096553569502</v>
+        <v>0.5915004111732658</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.690547462843806</v>
+        <v>0.5905943590109987</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6779784845007992</v>
+        <v>0.5895960205152344</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6816300113055136</v>
+        <v>0.5902225869312745</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6819432945135337</v>
+        <v>0.5881583150161598</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6810281362993846</v>
+        <v>0.5691546852037864</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6952116876876372</v>
+        <v>0.5903304586228008</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6801376694951464</v>
+        <v>0.5832107518656899</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6721430812918265</v>
+        <v>0.5771231810661366</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.606009153683538</v>
+        <v>0.5734989724170684</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6132666770335565</v>
+        <v>0.5824060920888022</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5983122633302093</v>
+        <v>0.5658306260340622</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5722031111876953</v>
+        <v>0.5655849377496285</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5508711339556269</v>
+        <v>0.5464525973962295</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5411931519687985</v>
+        <v>0.5485403349065789</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5227315073597913</v>
+        <v>0.5404781517796727</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5235023696748859</v>
+        <v>0.5325940620136143</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5357151612961975</v>
+        <v>0.5325940620136143</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5357151612961975</v>
+        <v>0.5617593452608604</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5486376996151643</v>
+        <v>0.5290388492191911</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5659955856662338</v>
+        <v>0.5534411419829619</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5413125813415596</v>
+        <v>0.5665690918184225</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5381459517995659</v>
+        <v>0.6278451158640033</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5368292517206936</v>
+        <v>0.6219785419389726</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5309768622226332</v>
+        <v>0.6280232092248508</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5313239428924463</v>
+        <v>0.6188495624191838</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5313239428924463</v>
+        <v>0.6195046728055466</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5299811504726041</v>
+        <v>0.6147781065295996</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5288203039740211</v>
+        <v>0.6123849660484357</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5331139825528046</v>
+        <v>0.6124525609720219</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5347556986373143</v>
+        <v>0.6032333839069446</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5243483569180077</v>
+        <v>0.6142841032149967</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5316240923717903</v>
+        <v>0.6139708200069767</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5262709596798032</v>
+        <v>0.5961656867153911</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5156128513009746</v>
+        <v>0.5967246582078449</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5411794928909753</v>
+        <v>0.608886841194658</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5663123712019007</v>
+        <v>0.6135613979050477</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5652529170886972</v>
+        <v>0.6039692229455695</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5652529170886972</v>
+        <v>0.6057722212182217</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5685885339396564</v>
+        <v>0.6209021015366814</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.579488478042507</v>
+        <v>0.6331695294692853</v>
       </c>
     </row>
     <row r="71">
@@ -1130,197 +1130,197 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.579488478042507</v>
+        <v>0.6287224489395652</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5695959784873026</v>
+        <v>0.6277852260612403</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5845465396302383</v>
+        <v>0.6394936825013904</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5794546805807139</v>
+        <v>0.6325065388457169</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5797185809689119</v>
+        <v>0.6233810490451954</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5665204094641298</v>
+        <v>0.606695084553194</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.562749278170272</v>
+        <v>0.6286989833443306</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5578355124815952</v>
+        <v>0.6275745610532759</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5470122693542128</v>
+        <v>0.6493691957675072</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5293200861292414</v>
+        <v>0.6648761016571614</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.529414999208474</v>
+        <v>0.6341767989005493</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5006097552433347</v>
+        <v>0.6220079614912071</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5006097552433347</v>
+        <v>0.6214151925369601</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4989757442796482</v>
+        <v>0.6058018158868383</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5028039635141515</v>
+        <v>0.5616744138154217</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5030834492603784</v>
+        <v>0.5411782670762989</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5012037500122581</v>
+        <v>0.5457734960654852</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5013051423976375</v>
+        <v>0.550466264879639</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4982490112929053</v>
+        <v>0.5168941778706128</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5018550078382092</v>
+        <v>0.5073343994418691</v>
       </c>
     </row>
   </sheetData>
